--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>要件ID</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>NOT_EXECUTED</t>
+  </si>
+  <si>
+    <t>AUTH-004</t>
+  </si>
+  <si>
+    <t>ログアウト</t>
   </si>
   <si>
     <t>REQ-USER-001</t>
@@ -555,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -648,41 +654,61 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -704,15 +730,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -720,7 +746,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -728,15 +754,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>要件ID</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>ログアウト</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>REQ-USER-001</t>
@@ -135,7 +138,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,6 +168,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -202,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -220,6 +228,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -668,25 +679,25 @@
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>17</v>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -694,19 +705,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>17</v>
@@ -730,15 +741,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -746,7 +757,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -754,7 +765,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -762,7 +773,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,90 +12,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
-  <si>
-    <t>要件ID</t>
-  </si>
-  <si>
-    <t>要件タイトル</t>
-  </si>
-  <si>
-    <t>テストケースID</t>
-  </si>
-  <si>
-    <t>テストケースタイトル</t>
-  </si>
-  <si>
-    <t>優先度</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+  <si>
+    <t>上流ID</t>
+  </si>
+  <si>
+    <t>機能名</t>
+  </si>
+  <si>
+    <t>TC-ID</t>
+  </si>
+  <si>
+    <t>テスト名</t>
+  </si>
+  <si>
+    <t>種別</t>
   </si>
   <si>
     <t>実行ステータス</t>
   </si>
   <si>
-    <t>REQ-LOGIN-001</t>
-  </si>
-  <si>
-    <t>ユーザーログイン機能</t>
-  </si>
-  <si>
-    <t>AUTH-001</t>
-  </si>
-  <si>
-    <t>正常ログイン</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>AUTH-002</t>
-  </si>
-  <si>
-    <t>誤パスワードによるログイン失敗</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>AUTH-003</t>
-  </si>
-  <si>
-    <t>アカウントロックアウト（連続失敗）</t>
+    <t>DD-001</t>
+  </si>
+  <si>
+    <t>ログイン・ログアウト機能</t>
+  </si>
+  <si>
+    <t>TC-001</t>
+  </si>
+  <si>
+    <t>正常系：正常ログイン</t>
+  </si>
+  <si>
+    <t>画面</t>
   </si>
   <si>
     <t>NOT_EXECUTED</t>
   </si>
   <si>
-    <t>AUTH-004</t>
-  </si>
-  <si>
-    <t>ログアウト</t>
-  </si>
-  <si>
-    <t>SKIP</t>
-  </si>
-  <si>
-    <t>REQ-USER-001</t>
-  </si>
-  <si>
-    <t>ユーザープロフィール管理</t>
-  </si>
-  <si>
-    <t>USER-001</t>
-  </si>
-  <si>
-    <t>ユーザープロフィール更新（正常）</t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>USER-002</t>
-  </si>
-  <si>
-    <t>無効メールアドレスへの更新バリデーション</t>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>異常系：誤パスワードによるログイン失敗</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>正常系：ログアウト</t>
+  </si>
+  <si>
+    <t>DD-002</t>
+  </si>
+  <si>
+    <t>ユーザープロフィール更新機能</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>(未定義)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TC-006</t>
   </si>
   <si>
     <t>項目</t>
@@ -104,16 +92,16 @@
     <t>値</t>
   </si>
   <si>
-    <t>要件総数</t>
-  </si>
-  <si>
-    <t>カバー済み要件</t>
+    <t>上流設計書 ID 総数</t>
+  </si>
+  <si>
+    <t>カバー済み上流ID</t>
   </si>
   <si>
     <t>テストケース総数</t>
   </si>
   <si>
-    <t>要件カバレッジ率 (%)</t>
+    <t>上流IDカバレッジ率 (%)</t>
   </si>
 </sst>
 </file>
@@ -138,7 +126,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,27 +140,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F7F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF4444"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -210,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -223,15 +196,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -575,10 +539,10 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
@@ -639,8 +603,8 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -651,16 +615,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>17</v>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -671,33 +635,33 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>20</v>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -705,22 +669,22 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
+      <c r="F7" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -735,21 +699,21 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -757,7 +721,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -765,15 +729,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>上流ID</t>
   </si>
@@ -59,7 +59,10 @@
     <t>TC-003</t>
   </si>
   <si>
-    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+    <t>(未定義)</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>TC-004</t>
@@ -75,12 +78,6 @@
   </si>
   <si>
     <t>TC-005</t>
-  </si>
-  <si>
-    <t>(未定義)</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>TC-006</t>
@@ -621,7 +618,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -635,10 +632,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
@@ -649,19 +646,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -669,19 +666,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -705,15 +702,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -721,7 +718,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -729,15 +726,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>上流ID</t>
   </si>
@@ -59,10 +59,7 @@
     <t>TC-003</t>
   </si>
   <si>
-    <t>(未定義)</t>
-  </si>
-  <si>
-    <t/>
+    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -80,7 +77,13 @@
     <t>TC-005</t>
   </si>
   <si>
+    <t>正常系：プロフィール更新</t>
+  </si>
+  <si>
     <t>TC-006</t>
+  </si>
+  <si>
+    <t>異常系：無効メールアドレスへの更新バリデーション</t>
   </si>
   <si>
     <t>項目</t>
@@ -618,7 +621,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -632,10 +635,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
@@ -646,19 +649,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -666,19 +669,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -702,15 +705,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -718,7 +721,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -726,15 +729,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>上流ID</t>
   </si>
@@ -59,7 +59,10 @@
     <t>TC-003</t>
   </si>
   <si>
-    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+    <t>(未定義)</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>TC-004</t>
@@ -621,7 +624,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -635,10 +638,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
@@ -649,16 +652,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
@@ -669,16 +672,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
@@ -705,15 +708,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -721,7 +724,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -729,15 +732,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>上流ID</t>
   </si>
@@ -59,10 +59,7 @@
     <t>TC-003</t>
   </si>
   <si>
-    <t>(未定義)</t>
-  </si>
-  <si>
-    <t/>
+    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -624,7 +621,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -638,10 +635,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
@@ -652,16 +649,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
@@ -672,16 +669,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
@@ -708,15 +705,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
         <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -724,7 +721,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -732,15 +729,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
   <si>
     <t>上流ID</t>
   </si>
@@ -47,19 +47,25 @@
     <t>画面</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>異常系：誤パスワードによるログイン失敗</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+  </si>
+  <si>
     <t>NOT_EXECUTED</t>
-  </si>
-  <si>
-    <t>TC-002</t>
-  </si>
-  <si>
-    <t>異常系：誤パスワードによるログイン失敗</t>
-  </si>
-  <si>
-    <t>TC-003</t>
-  </si>
-  <si>
-    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -126,7 +132,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,12 +146,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FF70AD47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -196,6 +212,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,8 +625,8 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -615,16 +637,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
+      <c r="F4" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -635,56 +657,56 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
+      <c r="F5" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>11</v>
+      <c r="F6" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>11</v>
+      <c r="F7" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -705,15 +727,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -721,7 +743,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -729,7 +751,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -737,7 +759,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>上流ID</t>
   </si>
@@ -65,25 +65,28 @@
     <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
   </si>
   <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>正常系：ログアウト</t>
+  </si>
+  <si>
+    <t>SKIP</t>
+  </si>
+  <si>
+    <t>DD-002</t>
+  </si>
+  <si>
+    <t>ユーザープロフィール更新機能</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>正常系：プロフィール更新</t>
+  </si>
+  <si>
     <t>NOT_EXECUTED</t>
-  </si>
-  <si>
-    <t>TC-004</t>
-  </si>
-  <si>
-    <t>正常系：ログアウト</t>
-  </si>
-  <si>
-    <t>DD-002</t>
-  </si>
-  <si>
-    <t>ユーザープロフィール更新機能</t>
-  </si>
-  <si>
-    <t>TC-005</t>
-  </si>
-  <si>
-    <t>正常系：プロフィール更新</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -132,7 +135,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,6 +160,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -199,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +225,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -645,8 +656,8 @@
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>17</v>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -657,16 +668,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -685,8 +696,8 @@
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>17</v>
+      <c r="F6" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -697,16 +708,16 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
+      <c r="F7" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -727,15 +738,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -743,7 +754,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -751,7 +762,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -759,7 +770,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
   <si>
     <t>上流ID</t>
   </si>
@@ -71,7 +71,7 @@
     <t>正常系：ログアウト</t>
   </si>
   <si>
-    <t>SKIP</t>
+    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>DD-002</t>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>正常系：プロフィール更新</t>
-  </si>
-  <si>
-    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -135,7 +132,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,11 +157,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF4444"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -207,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -225,9 +217,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -696,8 +685,8 @@
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>24</v>
+      <c r="F6" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -708,16 +697,16 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
+      <c r="F7" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -738,15 +727,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -754,7 +743,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -762,7 +751,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -770,7 +759,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>100</v>

--- a/reports/latest/traceability.xlsx
+++ b/reports/latest/traceability.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>上流ID</t>
   </si>
@@ -71,25 +71,28 @@
     <t>正常系：ログアウト</t>
   </si>
   <si>
+    <t>WAITING</t>
+  </si>
+  <si>
+    <t>DD-002</t>
+  </si>
+  <si>
+    <t>ユーザープロフィール更新機能</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>正常系：プロフィール更新</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>異常系：無効メールアドレスへの更新バリデーション</t>
+  </si>
+  <si>
     <t>NOT_EXECUTED</t>
-  </si>
-  <si>
-    <t>DD-002</t>
-  </si>
-  <si>
-    <t>ユーザープロフィール更新機能</t>
-  </si>
-  <si>
-    <t>TC-005</t>
-  </si>
-  <si>
-    <t>正常系：プロフィール更新</t>
-  </si>
-  <si>
-    <t>TC-006</t>
-  </si>
-  <si>
-    <t>異常系：無効メールアドレスへの更新バリデーション</t>
   </si>
   <si>
     <t>項目</t>
@@ -706,7 +709,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -727,15 +730,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -743,7 +746,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -751,7 +754,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -759,7 +762,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>100</v>
